--- a/Tendo_Monitoring_data/20260330_New_Tendo_Funnel_scorecard2_0_monthlydec25.xlsx
+++ b/Tendo_Monitoring_data/20260330_New_Tendo_Funnel_scorecard2_0_monthlydec25.xlsx
@@ -1,21 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tonikph-my.sharepoint.com/personal/dchakroborti_tonikbank_com/Documents/MyStuff/Data Engineering/Tendo_Model_Monitoring_Dashboards_Requirement/Tendo_Monitoring_data/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="11_D078C10752811878D2676A31F2F2D3C254D6FCAF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D8858982-3D36-42B1-BEB5-C3A302BF925C}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="New_Tendo_funnel_sc_2_0_rs" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -64,11 +58,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0.0%"/>
-  </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -78,13 +69,6 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -124,38 +108,27 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -193,7 +166,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -227,7 +200,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -262,10 +234,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -438,11 +409,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:G8"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -462,7 +433,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7">
       <c r="A2" s="1">
         <v>0</v>
       </c>
@@ -481,11 +452,11 @@
       <c r="F2">
         <v>8</v>
       </c>
-      <c r="G2" s="2">
+      <c r="G2">
         <v>0.5</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -499,16 +470,16 @@
         <v>71</v>
       </c>
       <c r="E3">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="F3">
-        <v>78</v>
-      </c>
-      <c r="G3" s="2">
-        <v>0.51</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+        <v>82</v>
+      </c>
+      <c r="G3">
+        <v>0.54</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -522,16 +493,16 @@
         <v>50</v>
       </c>
       <c r="E4">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F4">
         <v>60</v>
       </c>
-      <c r="G4" s="2">
+      <c r="G4">
         <v>0.64</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7">
       <c r="A5" s="1">
         <v>3</v>
       </c>
@@ -545,16 +516,16 @@
         <v>59</v>
       </c>
       <c r="E5">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="F5">
-        <v>77</v>
-      </c>
-      <c r="G5" s="2">
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+        <v>79</v>
+      </c>
+      <c r="G5">
+        <v>0.61</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
       <c r="A6" s="1">
         <v>4</v>
       </c>
@@ -568,16 +539,16 @@
         <v>34</v>
       </c>
       <c r="E6">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F6">
-        <v>26</v>
-      </c>
-      <c r="G6" s="2">
-        <v>0.53</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+      <c r="G6">
+        <v>0.59</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
       <c r="A7" s="1">
         <v>5</v>
       </c>
@@ -596,11 +567,11 @@
       <c r="F7">
         <v>43</v>
       </c>
-      <c r="G7" s="2">
+      <c r="G7">
         <v>0.65</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7">
       <c r="A8" s="1">
         <v>6</v>
       </c>
@@ -614,13 +585,13 @@
         <v>13</v>
       </c>
       <c r="E8">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F8">
-        <v>12</v>
-      </c>
-      <c r="G8" s="2">
-        <v>0.55000000000000004</v>
+        <v>13</v>
+      </c>
+      <c r="G8">
+        <v>0.59</v>
       </c>
     </row>
   </sheetData>
